--- a/data/trans_orig/P19C05-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19C05-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19113</t>
+          <t>20401</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15545</t>
+          <t>14873</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>12463</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28967</t>
+          <t>29164</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>340288</t>
+          <t>339000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>353553</t>
+          <t>353016</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>360707</t>
+          <t>361379</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>372058</t>
+          <t>372615</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>706686</t>
+          <t>706489</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>723669</t>
+          <t>723190</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12170</t>
+          <t>11411</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30208</t>
+          <t>30447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13572</t>
+          <t>13806</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31371</t>
+          <t>30829</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28471</t>
+          <t>28532</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55013</t>
+          <t>55370</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>545573</t>
+          <t>545334</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>563611</t>
+          <t>564370</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>516337</t>
+          <t>516879</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>534136</t>
+          <t>533902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1068476</t>
+          <t>1068119</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1095018</t>
+          <t>1094957</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23898</t>
+          <t>24259</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45267</t>
+          <t>47613</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37277</t>
+          <t>38807</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65916</t>
+          <t>65427</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>10,84%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>84316</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>68353</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>104063</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>7,62%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>6,18%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>10,92%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>84316</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>68095</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>103129</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>457666</t>
+          <t>455320</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479035</t>
+          <t>478674</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>537649</t>
+          <t>538138</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>566288</t>
+          <t>564758</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,47 +1582,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>93,57%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>979</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1022181</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1002434</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1038144</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>92,38%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>90,6%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>93,82%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>979</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1022181</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1003368</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1038402</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>90,68%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39745</t>
+          <t>39029</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67668</t>
+          <t>68032</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43137</t>
+          <t>43542</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70978</t>
+          <t>70170</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88320</t>
+          <t>89067</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127835</t>
+          <t>130085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>337080</t>
+          <t>336716</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365003</t>
+          <t>365719</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>368207</t>
+          <t>369015</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>396048</t>
+          <t>395643</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>716098</t>
+          <t>713848</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>755613</t>
+          <t>754866</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,45%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57570</t>
+          <t>58159</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86017</t>
+          <t>86675</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63522</t>
+          <t>61719</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95052</t>
+          <t>92589</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>129241</t>
+          <t>128158</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>168525</t>
+          <t>169212</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>186332</t>
+          <t>185674</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>214779</t>
+          <t>214190</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>224030</t>
+          <t>226493</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>255560</t>
+          <t>257363</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>422906</t>
+          <t>422219</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>462190</t>
+          <t>463273</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,33%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69371</t>
+          <t>69011</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97444</t>
+          <t>97738</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88272</t>
+          <t>88898</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>118171</t>
+          <t>118091</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>166469</t>
+          <t>165331</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>205374</t>
+          <t>205820</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,77%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>115321</t>
+          <t>115027</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>143394</t>
+          <t>143754</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>128767</t>
+          <t>128847</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158666</t>
+          <t>158040</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>254329</t>
+          <t>253883</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>293234</t>
+          <t>294372</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>64,04%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53087</t>
+          <t>49961</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74279</t>
+          <t>72877</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>112609</t>
+          <t>110586</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>140123</t>
+          <t>141888</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>169780</t>
+          <t>169901</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>206912</t>
+          <t>209355</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,5%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>52485</t>
+          <t>53887</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>73677</t>
+          <t>76803</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>68085</t>
+          <t>66320</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>95599</t>
+          <t>97622</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>128060</t>
+          <t>125617</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>165192</t>
+          <t>165071</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,28%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>301710</t>
+          <t>303299</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>365333</t>
+          <t>369199</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>404636</t>
+          <t>406123</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>484194</t>
+          <t>483010</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>729461</t>
+          <t>726894</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>831117</t>
+          <t>827500</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2089409</t>
+          <t>2085543</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2153032</t>
+          <t>2151443</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2256743</t>
+          <t>2257927</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2336301</t>
+          <t>2334814</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4364562</t>
+          <t>4368179</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4466218</t>
+          <t>4468785</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2012 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18538</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>8913</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23966</t>
+          <t>25116</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17185</t>
+          <t>17201</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36964</t>
+          <t>37430</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>360638</t>
+          <t>360010</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>372715</t>
+          <t>372756</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>347025</t>
+          <t>345875</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>362281</t>
+          <t>362078</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>713202</t>
+          <t>712736</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>732981</t>
+          <t>732965</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13830</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31020</t>
+          <t>30740</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23717</t>
+          <t>24765</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46154</t>
+          <t>49101</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42196</t>
+          <t>42154</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70742</t>
+          <t>71451</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>566247</t>
+          <t>566527</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>583437</t>
+          <t>583839</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512656</t>
+          <t>509709</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>535093</t>
+          <t>534045</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1085334</t>
+          <t>1084625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1113880</t>
+          <t>1113922</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33335</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61390</t>
+          <t>63243</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35084</t>
+          <t>35520</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64112</t>
+          <t>62874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76743</t>
+          <t>75197</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116930</t>
+          <t>114782</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>525261</t>
+          <t>523408</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>553316</t>
+          <t>552862</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>595342</t>
+          <t>596580</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>624370</t>
+          <t>623934</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1129174</t>
+          <t>1131322</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1169361</t>
+          <t>1170907</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60450</t>
+          <t>59457</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96874</t>
+          <t>96031</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69702</t>
+          <t>70086</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106071</t>
+          <t>105662</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139902</t>
+          <t>139374</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191320</t>
+          <t>190205</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>445965</t>
+          <t>446808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>482389</t>
+          <t>483382</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>457280</t>
+          <t>457689</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>493649</t>
+          <t>493265</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>914870</t>
+          <t>915985</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>966288</t>
+          <t>966816</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>79272</t>
+          <t>78579</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112186</t>
+          <t>111840</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77803</t>
+          <t>77042</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>112051</t>
+          <t>113566</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>164418</t>
+          <t>165536</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>216226</t>
+          <t>215419</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>249124</t>
+          <t>249470</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>282038</t>
+          <t>282731</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>278664</t>
+          <t>277149</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>312912</t>
+          <t>313673</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>535799</t>
+          <t>536606</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>587607</t>
+          <t>586489</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,99%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90652</t>
+          <t>89806</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123774</t>
+          <t>124124</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>112107</t>
+          <t>110058</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>146602</t>
+          <t>144275</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>207947</t>
+          <t>209453</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>257259</t>
+          <t>259684</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>138716</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>171838</t>
+          <t>172684</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153987</t>
+          <t>156314</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>188482</t>
+          <t>190531</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>305820</t>
+          <t>303395</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>355132</t>
+          <t>353626</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>62,8%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>69157</t>
+          <t>68313</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97985</t>
+          <t>96419</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>149432</t>
+          <t>151303</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>185092</t>
+          <t>185457</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>227142</t>
+          <t>225528</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>271669</t>
+          <t>274193</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>56,26%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>86941</t>
+          <t>88507</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>115769</t>
+          <t>116613</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>117321</t>
+          <t>116956</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>152981</t>
+          <t>151110</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>215670</t>
+          <t>213146</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>260197</t>
+          <t>261811</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,72%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>397309</t>
+          <t>400015</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>481554</t>
+          <t>479745</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>528109</t>
+          <t>529515</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>617858</t>
+          <t>620549</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>950909</t>
+          <t>952121</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1076018</t>
+          <t>1068420</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2433105</t>
+          <t>2434914</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2517350</t>
+          <t>2514644</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2528463</t>
+          <t>2525772</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2618212</t>
+          <t>2616806</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4984962</t>
+          <t>4992560</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5110071</t>
+          <t>5108859</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22645</t>
+          <t>22852</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>18121</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15356</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34974</t>
+          <t>35475</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>330195</t>
+          <t>329988</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>345253</t>
+          <t>345144</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>333803</t>
+          <t>333809</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>346343</t>
+          <t>346326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>669796</t>
+          <t>669295</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>689285</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>13652</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32382</t>
+          <t>32167</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>10606</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26363</t>
+          <t>26629</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,47 +7084,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>38785</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>27814</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>52518</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>5,31%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>38785</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>28257</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>52853</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>460696</t>
+          <t>460911</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>479549</t>
+          <t>479426</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>470357</t>
+          <t>470091</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>485884</t>
+          <t>486114</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,47 +7197,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>94,64%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>951012</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>937279</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>961983</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>94,69%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>951012</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>936944</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>961540</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>94,66%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14864</t>
+          <t>14443</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34844</t>
+          <t>34719</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28303</t>
+          <t>28155</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52835</t>
+          <t>51815</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47522</t>
+          <t>46401</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77347</t>
+          <t>78187</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>523016</t>
+          <t>523141</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542996</t>
+          <t>543417</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>520245</t>
+          <t>521265</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>544777</t>
+          <t>544925</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1053593</t>
+          <t>1052753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1083418</t>
+          <t>1084539</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36857</t>
+          <t>38408</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65346</t>
+          <t>66563</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39315</t>
+          <t>39386</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67337</t>
+          <t>65850</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83618</t>
+          <t>84375</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122052</t>
+          <t>125373</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>447026</t>
+          <t>445809</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>475515</t>
+          <t>473964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>477547</t>
+          <t>479034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>505569</t>
+          <t>505498</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>935204</t>
+          <t>931883</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>973638</t>
+          <t>972881</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49495</t>
+          <t>48663</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79547</t>
+          <t>81131</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52246</t>
+          <t>53235</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83125</t>
+          <t>85944</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112673</t>
+          <t>111650</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158587</t>
+          <t>157397</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>291455</t>
+          <t>289871</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>321507</t>
+          <t>322339</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>312748</t>
+          <t>309929</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>343627</t>
+          <t>342638</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>608288</t>
+          <t>609478</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>654202</t>
+          <t>655225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,44%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44699</t>
+          <t>44432</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72278</t>
+          <t>71334</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62265</t>
+          <t>61699</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>92667</t>
+          <t>91712</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114479</t>
+          <t>115852</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>157327</t>
+          <t>157428</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>157847</t>
+          <t>158791</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>185426</t>
+          <t>185693</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>184281</t>
+          <t>185236</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>214683</t>
+          <t>215249</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>349747</t>
+          <t>349646</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>392595</t>
+          <t>391222</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42789</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63207</t>
+          <t>64137</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56178</t>
+          <t>55414</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88242</t>
+          <t>88065</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>102792</t>
+          <t>103746</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142209</t>
+          <t>143103</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>83850</t>
+          <t>82920</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>104268</t>
+          <t>104952</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>139637</t>
+          <t>139814</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>171701</t>
+          <t>172465</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>232727</t>
+          <t>231833</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>272144</t>
+          <t>271190</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,33%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>251292</t>
+          <t>253386</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>316354</t>
+          <t>318699</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>299632</t>
+          <t>296557</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>371248</t>
+          <t>369711</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>571410</t>
+          <t>570141</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>669867</t>
+          <t>667864</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2347979</t>
+          <t>2345634</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2413041</t>
+          <t>2410947</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2496067</t>
+          <t>2497604</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2567683</t>
+          <t>2570758</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4861781</t>
+          <t>4863784</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4960238</t>
+          <t>4961507</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>333</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18929</t>
+          <t>22300</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>324</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15771</t>
+          <t>15030</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25817</t>
+          <t>25955</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>364518</t>
+          <t>361147</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383137</t>
+          <t>383114</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287770</t>
+          <t>288511</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303303</t>
+          <t>303217</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>661171</t>
+          <t>661033</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>684432</t>
+          <t>684476</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>9449</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27837</t>
+          <t>32563</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9167</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29847</t>
+          <t>31178</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>22822</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52183</t>
+          <t>51591</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>374514</t>
+          <t>369788</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>393742</t>
+          <t>392902</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>469845</t>
+          <t>468514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490525</t>
+          <t>490591</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>849859</t>
+          <t>850451</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>880378</t>
+          <t>879220</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13175</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31285</t>
+          <t>32527</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17528</t>
+          <t>17425</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32291</t>
+          <t>32735</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34159</t>
+          <t>33811</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58349</t>
+          <t>58244</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>492757</t>
+          <t>491515</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>510867</t>
+          <t>510839</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>499590</t>
+          <t>499146</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514353</t>
+          <t>514456</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>997574</t>
+          <t>997679</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1021764</t>
+          <t>1022112</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19781</t>
+          <t>19851</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76651</t>
+          <t>74954</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36239</t>
+          <t>36553</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57841</t>
+          <t>57471</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56490</t>
+          <t>54239</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121587</t>
+          <t>124069</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>786277</t>
+          <t>787974</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>843147</t>
+          <t>843077</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>642751</t>
+          <t>643121</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>664353</t>
+          <t>664039</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1441932</t>
+          <t>1439450</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1507029</t>
+          <t>1509280</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50302</t>
+          <t>50645</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76840</t>
+          <t>77459</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42346</t>
+          <t>40685</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62564</t>
+          <t>61730</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96703</t>
+          <t>98167</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130329</t>
+          <t>129450</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>469739</t>
+          <t>469120</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>496277</t>
+          <t>495934</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>471962</t>
+          <t>472796</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>492180</t>
+          <t>493841</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>950776</t>
+          <t>951655</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>984402</t>
+          <t>982938</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,92%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54702</t>
+          <t>56153</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79010</t>
+          <t>80818</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36096</t>
+          <t>38353</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>143766</t>
+          <t>145952</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79914</t>
+          <t>80002</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>207606</t>
+          <t>207369</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280343</t>
+          <t>278535</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>304651</t>
+          <t>303200</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>456143</t>
+          <t>453957</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>563813</t>
+          <t>561556</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>751656</t>
+          <t>751893</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>879348</t>
+          <t>879260</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86780</t>
+          <t>85279</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111247</t>
+          <t>111684</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>149238</t>
+          <t>150082</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>177906</t>
+          <t>176423</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>242600</t>
+          <t>241857</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>280881</t>
+          <t>280615</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>164274</t>
+          <t>163837</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>188741</t>
+          <t>190242</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>230781</t>
+          <t>232264</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>259449</t>
+          <t>258605</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>403327</t>
+          <t>403593</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>441608</t>
+          <t>442351</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,65%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>244798</t>
+          <t>247443</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>361711</t>
+          <t>360860</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>312993</t>
+          <t>326155</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>437865</t>
+          <t>438160</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>620979</t>
+          <t>622322</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>785501</t>
+          <t>779952</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2992510</t>
+          <t>2993361</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3109423</t>
+          <t>3106778</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3140962</t>
+          <t>3140667</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3265834</t>
+          <t>3252672</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6147547</t>
+          <t>6153096</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6312069</t>
+          <t>6310726</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C05-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19C05-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20401</t>
+          <t>19064</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14873</t>
+          <t>14823</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12463</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29164</t>
+          <t>29486</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>339000</t>
+          <t>340337</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>353016</t>
+          <t>353212</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>361379</t>
+          <t>361429</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>372615</t>
+          <t>372684</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>706489</t>
+          <t>706167</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>723190</t>
+          <t>722825</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11411</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30447</t>
+          <t>30237</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13806</t>
+          <t>13216</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30829</t>
+          <t>32419</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28532</t>
+          <t>28455</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55370</t>
+          <t>54485</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>545334</t>
+          <t>545544</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>564370</t>
+          <t>564120</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>516879</t>
+          <t>515289</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>533902</t>
+          <t>534492</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1068119</t>
+          <t>1069004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1094957</t>
+          <t>1095034</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24259</t>
+          <t>23959</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47613</t>
+          <t>47494</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38807</t>
+          <t>38131</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65427</t>
+          <t>65215</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68353</t>
+          <t>68816</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104063</t>
+          <t>106330</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>455320</t>
+          <t>455439</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>478674</t>
+          <t>478974</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>538138</t>
+          <t>538350</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>564758</t>
+          <t>565434</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1002434</t>
+          <t>1000167</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1038144</t>
+          <t>1037681</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39029</t>
+          <t>39519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68032</t>
+          <t>68394</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43542</t>
+          <t>42798</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70170</t>
+          <t>69730</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89067</t>
+          <t>89837</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130085</t>
+          <t>131186</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>336716</t>
+          <t>336354</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365719</t>
+          <t>365229</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>369015</t>
+          <t>369455</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>395643</t>
+          <t>396387</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>713848</t>
+          <t>712747</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>754866</t>
+          <t>754096</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,36%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58159</t>
+          <t>57554</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86675</t>
+          <t>85894</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61719</t>
+          <t>62369</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92589</t>
+          <t>91855</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128158</t>
+          <t>126773</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169212</t>
+          <t>170269</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185674</t>
+          <t>186455</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>214190</t>
+          <t>214795</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>226493</t>
+          <t>227227</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>257363</t>
+          <t>256713</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>422219</t>
+          <t>421162</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>463273</t>
+          <t>464658</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,56%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69011</t>
+          <t>69434</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97738</t>
+          <t>95951</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88898</t>
+          <t>89716</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>118091</t>
+          <t>119256</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>165331</t>
+          <t>164082</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>205820</t>
+          <t>204870</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>115027</t>
+          <t>116814</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>143754</t>
+          <t>143331</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>128847</t>
+          <t>127682</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158040</t>
+          <t>157222</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>253883</t>
+          <t>254833</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>294372</t>
+          <t>295621</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,31%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49961</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72877</t>
+          <t>74526</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>110586</t>
+          <t>110854</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>141888</t>
+          <t>140549</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>169901</t>
+          <t>170966</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>209355</t>
+          <t>207021</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>61,8%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>53887</t>
+          <t>52238</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>76803</t>
+          <t>75015</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>66320</t>
+          <t>67659</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>97622</t>
+          <t>97354</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>125617</t>
+          <t>127951</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>165071</t>
+          <t>164006</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>48,96%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>303299</t>
+          <t>299928</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>369199</t>
+          <t>369344</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>406123</t>
+          <t>403825</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>483010</t>
+          <t>477766</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>726894</t>
+          <t>722756</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>827500</t>
+          <t>825630</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2085543</t>
+          <t>2085398</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2151443</t>
+          <t>2154814</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2257927</t>
+          <t>2263171</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2334814</t>
+          <t>2337112</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4368179</t>
+          <t>4370049</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4468785</t>
+          <t>4472923</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19166</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,82 +3727,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>4,79%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>14937</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8794</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>24314</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>6,55%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>26118</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>17440</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>37905</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>5,05%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14937</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8913</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>25116</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>26118</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>17201</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>37430</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>360010</t>
+          <t>361026</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>372756</t>
+          <t>373359</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,82 +3840,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>95,21%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>356054</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>346677</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>362197</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>95,97%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>93,45%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>97,63%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>724048</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>712261</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>732726</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>96,52%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>94,95%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>356054</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>345875</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>362078</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,97%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>93,23%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>97,6%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>709</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>724048</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>712736</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>732965</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,52%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>95,01%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13428</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30740</t>
+          <t>31914</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24765</t>
+          <t>24225</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49101</t>
+          <t>49726</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42154</t>
+          <t>42320</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71451</t>
+          <t>69497</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>566527</t>
+          <t>565353</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>583839</t>
+          <t>583634</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>509709</t>
+          <t>509084</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>534045</t>
+          <t>534585</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1084625</t>
+          <t>1086579</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1113922</t>
+          <t>1113756</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>32947</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63243</t>
+          <t>60054</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35520</t>
+          <t>36811</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62874</t>
+          <t>64917</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75197</t>
+          <t>76456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114782</t>
+          <t>117875</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>523408</t>
+          <t>526597</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>552862</t>
+          <t>553704</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>596580</t>
+          <t>594537</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>623934</t>
+          <t>622643</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1131322</t>
+          <t>1128229</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1170907</t>
+          <t>1169648</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59457</t>
+          <t>58286</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96031</t>
+          <t>95848</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70086</t>
+          <t>70569</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105662</t>
+          <t>104931</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139374</t>
+          <t>141643</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>190205</t>
+          <t>192974</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>446808</t>
+          <t>446991</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>483382</t>
+          <t>484553</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>457689</t>
+          <t>458420</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>493265</t>
+          <t>492782</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>915985</t>
+          <t>913216</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>966816</t>
+          <t>964547</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,2%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78579</t>
+          <t>78318</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111840</t>
+          <t>113097</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77042</t>
+          <t>78920</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>113566</t>
+          <t>112632</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>165536</t>
+          <t>165210</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>215419</t>
+          <t>215812</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>249470</t>
+          <t>248213</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>282731</t>
+          <t>282992</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>277149</t>
+          <t>278083</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>313673</t>
+          <t>311795</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>536606</t>
+          <t>536213</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>586489</t>
+          <t>586815</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,03%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89806</t>
+          <t>88650</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124124</t>
+          <t>123890</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>110058</t>
+          <t>108911</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>144275</t>
+          <t>144677</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>209453</t>
+          <t>210902</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>259684</t>
+          <t>257995</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,82%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>138366</t>
+          <t>138600</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>172684</t>
+          <t>173840</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>156314</t>
+          <t>155912</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>190531</t>
+          <t>191678</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>303395</t>
+          <t>305084</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>353626</t>
+          <t>352177</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,54%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68313</t>
+          <t>69478</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96419</t>
+          <t>96702</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>151303</t>
+          <t>149022</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>185457</t>
+          <t>184996</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>225528</t>
+          <t>228132</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>274193</t>
+          <t>274306</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,29%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>88507</t>
+          <t>88224</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>116613</t>
+          <t>115448</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>116956</t>
+          <t>117417</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>151110</t>
+          <t>153391</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>213146</t>
+          <t>213033</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>261811</t>
+          <t>259207</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,19%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>400015</t>
+          <t>400853</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>479745</t>
+          <t>482157</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>529515</t>
+          <t>526808</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>620549</t>
+          <t>614330</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>952121</t>
+          <t>949783</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1068420</t>
+          <t>1070834</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2434914</t>
+          <t>2432502</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2514644</t>
+          <t>2513806</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2525772</t>
+          <t>2531991</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2616806</t>
+          <t>2619513</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4992560</t>
+          <t>4990146</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5108859</t>
+          <t>5111197</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,33%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>21738</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18121</t>
+          <t>18385</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15485</t>
+          <t>16069</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35475</t>
+          <t>35108</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>329988</t>
+          <t>331102</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>345144</t>
+          <t>345921</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>333809</t>
+          <t>333545</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>346326</t>
+          <t>346532</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>669295</t>
+          <t>669662</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>689285</t>
+          <t>688701</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13652</t>
+          <t>13328</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32167</t>
+          <t>33779</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26629</t>
+          <t>26989</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27814</t>
+          <t>26393</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52518</t>
+          <t>51632</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>460911</t>
+          <t>459299</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>479426</t>
+          <t>479750</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>470091</t>
+          <t>469731</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>486114</t>
+          <t>485738</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>937279</t>
+          <t>938165</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>961983</t>
+          <t>963404</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14443</t>
+          <t>15596</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34719</t>
+          <t>37065</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28155</t>
+          <t>28365</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51815</t>
+          <t>51126</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46401</t>
+          <t>48321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78187</t>
+          <t>76554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>523141</t>
+          <t>520795</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>543417</t>
+          <t>542264</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>521265</t>
+          <t>521954</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>544925</t>
+          <t>544715</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1052753</t>
+          <t>1054386</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1084539</t>
+          <t>1082619</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38408</t>
+          <t>37847</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66563</t>
+          <t>66877</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39386</t>
+          <t>39358</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65850</t>
+          <t>68115</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84375</t>
+          <t>84020</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125373</t>
+          <t>122522</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>445809</t>
+          <t>445495</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>473964</t>
+          <t>474525</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>479034</t>
+          <t>476769</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>505498</t>
+          <t>505526</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>931883</t>
+          <t>934734</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>972881</t>
+          <t>973236</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,05%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48663</t>
+          <t>49935</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81131</t>
+          <t>79970</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53235</t>
+          <t>54297</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85944</t>
+          <t>86866</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111650</t>
+          <t>113214</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>157397</t>
+          <t>156664</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>289871</t>
+          <t>291032</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>322339</t>
+          <t>321067</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>309929</t>
+          <t>309007</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>342638</t>
+          <t>341576</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>609478</t>
+          <t>610211</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>655225</t>
+          <t>653661</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,24%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44432</t>
+          <t>44571</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71334</t>
+          <t>73199</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61699</t>
+          <t>61804</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91712</t>
+          <t>90545</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115852</t>
+          <t>114135</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>157428</t>
+          <t>156487</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>158791</t>
+          <t>156926</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>185693</t>
+          <t>185554</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>185236</t>
+          <t>186403</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>215249</t>
+          <t>215144</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>349646</t>
+          <t>350587</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>391222</t>
+          <t>392939</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42105</t>
+          <t>42320</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64137</t>
+          <t>64099</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55414</t>
+          <t>55714</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88065</t>
+          <t>88021</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>103746</t>
+          <t>103772</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>143103</t>
+          <t>143759</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,34%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>82920</t>
+          <t>82958</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>104952</t>
+          <t>104737</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>139814</t>
+          <t>139858</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>172465</t>
+          <t>172165</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>231833</t>
+          <t>231177</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>271190</t>
+          <t>271164</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,32%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>253386</t>
+          <t>254844</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>318699</t>
+          <t>317446</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>296557</t>
+          <t>298011</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>369711</t>
+          <t>372425</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>570141</t>
+          <t>574241</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>667864</t>
+          <t>672027</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2345634</t>
+          <t>2346887</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2410947</t>
+          <t>2409489</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2497604</t>
+          <t>2494890</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2570758</t>
+          <t>2569304</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4863784</t>
+          <t>4859621</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4961507</t>
+          <t>4957407</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,62%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22300</t>
+          <t>25769</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15030</t>
+          <t>21173</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9178</t>
+          <t>14493</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25955</t>
+          <t>32653</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>378122</t>
+          <t>370706</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>361147</t>
+          <t>353085</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383114</t>
+          <t>377657</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>299687</t>
+          <t>336895</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>288511</t>
+          <t>322067</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303217</t>
+          <t>341904</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>677810</t>
+          <t>707601</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>661033</t>
+          <t>689441</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>684476</t>
+          <t>717080</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9449</t>
+          <t>10908</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32563</t>
+          <t>34604</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18169</t>
+          <t>19573</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31178</t>
+          <t>31674</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>35305</t>
+          <t>39503</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22822</t>
+          <t>26933</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51591</t>
+          <t>56634</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>385214</t>
+          <t>425962</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369788</t>
+          <t>411289</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>392902</t>
+          <t>434985</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>481523</t>
+          <t>463036</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>468514</t>
+          <t>450935</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490591</t>
+          <t>470747</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>866737</t>
+          <t>888999</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>850451</t>
+          <t>871868</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>879220</t>
+          <t>901569</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20592</t>
+          <t>23044</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>14620</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32527</t>
+          <t>34244</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24459</t>
+          <t>28263</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17425</t>
+          <t>20781</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32735</t>
+          <t>38579</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>45052</t>
+          <t>51307</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33811</t>
+          <t>40485</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58244</t>
+          <t>66787</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>503450</t>
+          <t>578080</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>491515</t>
+          <t>566880</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>510839</t>
+          <t>586504</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>507422</t>
+          <t>579019</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>499146</t>
+          <t>568703</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514456</t>
+          <t>586501</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1010871</t>
+          <t>1157098</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>997679</t>
+          <t>1141618</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1022112</t>
+          <t>1167920</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>601124</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>601124</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>601124</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1055923</t>
+          <t>1208405</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1055923</t>
+          <t>1208405</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1055923</t>
+          <t>1208405</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49094</t>
+          <t>51598</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>38593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74954</t>
+          <t>66814</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>7,61%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>5,69%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>46290</t>
+          <t>49963</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>38509</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57471</t>
+          <t>60469</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>95384</t>
+          <t>101561</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54239</t>
+          <t>84588</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124069</t>
+          <t>119952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -10807,34 +10807,34 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>813834</t>
+          <t>626701</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>787974</t>
+          <t>611485</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>843077</t>
+          <t>639706</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>92,39%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,15%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>94,31%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,31%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,7%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>1037</t>
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>654302</t>
+          <t>671794</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>643121</t>
+          <t>661288</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>664039</t>
+          <t>683248</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1468135</t>
+          <t>1298495</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1439450</t>
+          <t>1280104</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1509280</t>
+          <t>1315468</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>62990</t>
+          <t>70291</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50645</t>
+          <t>57039</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77459</t>
+          <t>85991</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>50949</t>
+          <t>60434</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40685</t>
+          <t>50303</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61730</t>
+          <t>71935</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>113939</t>
+          <t>130725</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98167</t>
+          <t>114569</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129450</t>
+          <t>151215</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>483589</t>
+          <t>523064</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>469120</t>
+          <t>507364</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>495934</t>
+          <t>536316</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>483577</t>
+          <t>535415</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>472796</t>
+          <t>523914</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>493841</t>
+          <t>545546</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>967166</t>
+          <t>1058479</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>951655</t>
+          <t>1037989</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>982938</t>
+          <t>1074635</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,37%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>66793</t>
+          <t>71842</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56153</t>
+          <t>60588</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80818</t>
+          <t>85391</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>91482</t>
+          <t>98578</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38353</t>
+          <t>86416</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>145952</t>
+          <t>111185</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>158275</t>
+          <t>170420</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80002</t>
+          <t>153599</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>207369</t>
+          <t>188495</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>292560</t>
+          <t>325902</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>278535</t>
+          <t>312353</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>303200</t>
+          <t>337156</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>508427</t>
+          <t>330347</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>453957</t>
+          <t>317740</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>561556</t>
+          <t>342509</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>800987</t>
+          <t>656249</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>751893</t>
+          <t>638174</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>879260</t>
+          <t>673070</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>81,42%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>98685</t>
+          <t>107484</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85279</t>
+          <t>94642</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111684</t>
+          <t>121052</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>162727</t>
+          <t>174377</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>150082</t>
+          <t>159226</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>176423</t>
+          <t>190020</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>261412</t>
+          <t>281861</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>241857</t>
+          <t>261984</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>280615</t>
+          <t>303160</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>176836</t>
+          <t>194925</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>163837</t>
+          <t>181357</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>190242</t>
+          <t>207767</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>245960</t>
+          <t>271409</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>232264</t>
+          <t>255766</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>258605</t>
+          <t>286560</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>422796</t>
+          <t>466335</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>403593</t>
+          <t>445036</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>442351</t>
+          <t>486212</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,98%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>684208</t>
+          <t>748196</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>684208</t>
+          <t>748196</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>684208</t>
+          <t>748196</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>320615</t>
+          <t>352339</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>247443</t>
+          <t>318270</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>360860</t>
+          <t>390567</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>397930</t>
+          <t>437533</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>326155</t>
+          <t>410127</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>438160</t>
+          <t>473377</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>718545</t>
+          <t>789872</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>622322</t>
+          <t>746058</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>779952</t>
+          <t>843528</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3033606</t>
+          <t>3045339</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2993361</t>
+          <t>3007111</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3106778</t>
+          <t>3079408</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3180897</t>
+          <t>3187915</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3140667</t>
+          <t>3152071</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3252672</t>
+          <t>3215321</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6214503</t>
+          <t>6233253</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6153096</t>
+          <t>6179597</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6310726</t>
+          <t>6277067</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
